--- a/forms/trg/Formulir_TRG_mediacom.xlsx
+++ b/forms/trg/Formulir_TRG_mediacom.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,26 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Jeanny Maria Fatimah, M.Si.</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="n"/>
+          <t>Lecture Team</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Cultural Communication</t>
-        </is>
-      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>6019838</t>
-        </is>
-      </c>
+      <c r="K5" s="12" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
         <is>
@@ -946,14 +942,14 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Arianto, S.Sos. M.Si.</t>
+          <t>Prof. Dr. Jeanny Maria Fatimah, M.Si.</t>
         </is>
       </c>
       <c r="C6" s="12" t="n"/>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Media and Communication</t>
+          <t>Cultural Communication</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -961,7 +957,11 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>6019838</t>
+        </is>
+      </c>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
@@ -975,14 +975,14 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Zeti Azreen Ahmad (Assoc. Prof.Dr.)</t>
+          <t>Prof. Dr. Arianto, S.Sos. M.Si.</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>Media and Communication</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1004,14 +1004,18 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Andi Nur Fitrah, S.I.Kom., M.I.Kom.</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n"/>
+          <t>Zeti Azreen Ahmad (Assoc. Prof.Dr.)</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>External Collaborator</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1033,10 +1037,14 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Andi Nur Aisyah Rusnali, S.I.Kom., M.I.Kom.</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n"/>
+          <t>Andi Nur Fitrah, S.I.Kom., M.I.Kom.</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>External collaborator</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
@@ -1062,16 +1070,20 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Andi Nur</t>
+          <t>Andi Nur Aisyah Rusnali, S.I.Kom., M.I.Kom.</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1091,12 +1103,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Nurazizah Lutfiah</t>
+          <t>Andi Nur</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1120,12 +1132,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Xxx</t>
+          <t>Nurazizah Lutfiah</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1147,8 +1159,16 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Xxx</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
@@ -1158,7 +1178,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1347,15 +1371,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
